--- a/TIME TABLE SAMPLE DATA/SUBJECT ID MAPPING.xlsx
+++ b/TIME TABLE SAMPLE DATA/SUBJECT ID MAPPING.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ganig\Desktop\Time_Table_\TIME TABLE SAMPLE DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44DF595C-2A03-421C-ABF5-4ACF29DC643C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F8D54C-EA9F-4E53-9D58-1AFE04094651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{D5835059-CC22-4E12-ADB8-D8135E19DFD9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D5835059-CC22-4E12-ADB8-D8135E19DFD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>subject name</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>TECHNICAL</t>
+  </si>
+  <si>
+    <t>CNS</t>
   </si>
 </sst>
 </file>
@@ -476,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D29FDEDE-F9BD-4415-A9EB-A30740593BED}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -658,6 +661,14 @@
         <v>21</v>
       </c>
     </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TIME TABLE SAMPLE DATA/SUBJECT ID MAPPING.xlsx
+++ b/TIME TABLE SAMPLE DATA/SUBJECT ID MAPPING.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ganig\Desktop\Time_Table_\TIME TABLE SAMPLE DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F8D54C-EA9F-4E53-9D58-1AFE04094651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{C9F8D54C-EA9F-4E53-9D58-1AFE04094651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF3C7E00-AA41-4882-87B9-F062BE536CC9}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D5835059-CC22-4E12-ADB8-D8135E19DFD9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D5835059-CC22-4E12-ADB8-D8135E19DFD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>subject name</t>
   </si>
@@ -108,6 +106,9 @@
   </si>
   <si>
     <t>CNS</t>
+  </si>
+  <si>
+    <t>SPORTS</t>
   </si>
 </sst>
 </file>
@@ -160,6 +161,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -479,13 +484,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D29FDEDE-F9BD-4415-A9EB-A30740593BED}">
-  <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -493,7 +498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -501,7 +506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -509,7 +514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -517,7 +522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -525,7 +530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -533,7 +538,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -541,7 +546,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -549,7 +554,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -557,7 +562,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -565,7 +570,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -573,7 +578,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -581,7 +586,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -589,7 +594,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -597,7 +602,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -605,7 +610,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -613,7 +618,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -621,7 +626,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -629,7 +634,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -637,7 +642,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -645,7 +650,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -653,7 +658,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -661,12 +666,20 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
       <c r="B23">
         <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/TIME TABLE SAMPLE DATA/SUBJECT ID MAPPING.xlsx
+++ b/TIME TABLE SAMPLE DATA/SUBJECT ID MAPPING.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5afc8f5c19c83632/Desktop/Timetable/TIME TABLE SAMPLE DATA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ganig\Desktop\Time_Table_\TIME TABLE SAMPLE DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{C9F8D54C-EA9F-4E53-9D58-1AFE04094651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF3C7E00-AA41-4882-87B9-F062BE536CC9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29853E9E-FB97-4D25-9FE1-56AED06E1222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D5835059-CC22-4E12-ADB8-D8135E19DFD9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D5835059-CC22-4E12-ADB8-D8135E19DFD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>subject name</t>
   </si>
@@ -72,12 +72,6 @@
     <t>OS LAB</t>
   </si>
   <si>
-    <t>VERBAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APTITUDE </t>
-  </si>
-  <si>
     <t xml:space="preserve">CD </t>
   </si>
   <si>
@@ -102,13 +96,13 @@
     <t>CC LAB</t>
   </si>
   <si>
-    <t>TECHNICAL</t>
-  </si>
-  <si>
     <t>CNS</t>
   </si>
   <si>
     <t>SPORTS</t>
+  </si>
+  <si>
+    <t>TPW</t>
   </si>
 </sst>
 </file>
@@ -161,10 +155,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -484,13 +474,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D29FDEDE-F9BD-4415-A9EB-A30740593BED}">
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -506,7 +496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -514,7 +504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -522,7 +512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -530,7 +520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -538,7 +528,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -546,7 +536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -554,7 +544,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -562,7 +552,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -570,7 +560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -578,23 +568,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -602,7 +592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -610,76 +600,60 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22">
         <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
